--- a/data/nzd0196/nzd0196.xlsx
+++ b/data/nzd0196/nzd0196.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O625"/>
+  <dimension ref="A1:O626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32265,6 +32265,57 @@
       <c r="O625" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>343.1</v>
+      </c>
+      <c r="C626" t="n">
+        <v>317.33</v>
+      </c>
+      <c r="D626" t="n">
+        <v>356.21</v>
+      </c>
+      <c r="E626" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="F626" t="n">
+        <v>356.68</v>
+      </c>
+      <c r="G626" t="n">
+        <v>357.02</v>
+      </c>
+      <c r="H626" t="n">
+        <v>333.01</v>
+      </c>
+      <c r="I626" t="n">
+        <v>343.9</v>
+      </c>
+      <c r="J626" t="n">
+        <v>357.44</v>
+      </c>
+      <c r="K626" t="n">
+        <v>360.55</v>
+      </c>
+      <c r="L626" t="n">
+        <v>312.55</v>
+      </c>
+      <c r="M626" t="n">
+        <v>296.36</v>
+      </c>
+      <c r="N626" t="n">
+        <v>279.69</v>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -32279,7 +32330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B632"/>
+  <dimension ref="A1:B633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38602,6 +38653,16 @@
       </c>
       <c r="B632" t="n">
         <v>1.61</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -38770,28 +38831,28 @@
         <v>0.0824</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.155609425130573</v>
+        <v>-0.1586531750820686</v>
       </c>
       <c r="J2" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K2" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01509391800504867</v>
+        <v>0.01570819127579381</v>
       </c>
       <c r="M2" t="n">
-        <v>7.700507664069774</v>
+        <v>7.702435746899327</v>
       </c>
       <c r="N2" t="n">
-        <v>89.76989630604797</v>
+        <v>89.77772140282583</v>
       </c>
       <c r="O2" t="n">
-        <v>9.474697689427773</v>
+        <v>9.475110627471631</v>
       </c>
       <c r="P2" t="n">
-        <v>356.9430784400133</v>
+        <v>356.9736803432426</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38848,28 +38909,28 @@
         <v>0.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09796980197250091</v>
+        <v>0.09031578113841657</v>
       </c>
       <c r="J3" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K3" t="n">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001232615330203135</v>
+        <v>0.001049095526386101</v>
       </c>
       <c r="M3" t="n">
-        <v>17.65759780822611</v>
+        <v>17.67042790193748</v>
       </c>
       <c r="N3" t="n">
-        <v>437.891849718578</v>
+        <v>438.1380738769571</v>
       </c>
       <c r="O3" t="n">
-        <v>20.92586556677114</v>
+        <v>20.93174798904662</v>
       </c>
       <c r="P3" t="n">
-        <v>339.1272646568964</v>
+        <v>339.2047704895372</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38926,28 +38987,28 @@
         <v>0.0453</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2127923902683932</v>
+        <v>0.210946375346973</v>
       </c>
       <c r="J4" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K4" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02715069107303059</v>
+        <v>0.02676863526269913</v>
       </c>
       <c r="M4" t="n">
-        <v>7.859962076486362</v>
+        <v>7.857479121526288</v>
       </c>
       <c r="N4" t="n">
-        <v>91.90386483185969</v>
+        <v>91.81248224018516</v>
       </c>
       <c r="O4" t="n">
-        <v>9.586650344716849</v>
+        <v>9.58188302162916</v>
       </c>
       <c r="P4" t="n">
-        <v>356.5300555830825</v>
+        <v>356.5486379795953</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39004,28 +39065,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1929838269439731</v>
+        <v>0.1931644834464704</v>
       </c>
       <c r="J5" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K5" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02841503992391359</v>
+        <v>0.02856251433430168</v>
       </c>
       <c r="M5" t="n">
-        <v>6.890820409094007</v>
+        <v>6.880600401832926</v>
       </c>
       <c r="N5" t="n">
-        <v>72.3380651682437</v>
+        <v>72.2224879116404</v>
       </c>
       <c r="O5" t="n">
-        <v>8.505178726413908</v>
+        <v>8.49838148776815</v>
       </c>
       <c r="P5" t="n">
-        <v>359.2566477018028</v>
+        <v>359.2548310100523</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39082,28 +39143,28 @@
         <v>0.0466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04716180163277686</v>
+        <v>0.04661116353248974</v>
       </c>
       <c r="J6" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K6" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001404162861816549</v>
+        <v>0.001376287712573365</v>
       </c>
       <c r="M6" t="n">
-        <v>7.557432081844717</v>
+        <v>7.548093837030768</v>
       </c>
       <c r="N6" t="n">
-        <v>89.85569142084155</v>
+        <v>89.7164329646377</v>
       </c>
       <c r="O6" t="n">
-        <v>9.47922419931302</v>
+        <v>9.471875894702046</v>
       </c>
       <c r="P6" t="n">
-        <v>357.2105276350598</v>
+        <v>357.2160648821587</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39160,28 +39221,28 @@
         <v>0.0487</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01579177185945112</v>
+        <v>-0.01655121824314089</v>
       </c>
       <c r="J7" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K7" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002376279771798551</v>
+        <v>0.0002618911351297548</v>
       </c>
       <c r="M7" t="n">
-        <v>6.176128575359778</v>
+        <v>6.169699489249738</v>
       </c>
       <c r="N7" t="n">
-        <v>59.60099162162946</v>
+        <v>59.51478211530231</v>
       </c>
       <c r="O7" t="n">
-        <v>7.720167849317103</v>
+        <v>7.714582432983804</v>
       </c>
       <c r="P7" t="n">
-        <v>359.8654204013501</v>
+        <v>359.8730574360607</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39238,28 +39299,28 @@
         <v>0.0425</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2329133702386833</v>
+        <v>-0.2330088868071059</v>
       </c>
       <c r="J8" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K8" t="n">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0173018459573403</v>
+        <v>0.01737482856475814</v>
       </c>
       <c r="M8" t="n">
-        <v>10.61025358499061</v>
+        <v>10.59371895193605</v>
       </c>
       <c r="N8" t="n">
-        <v>175.0286267351625</v>
+        <v>174.7478315230197</v>
       </c>
       <c r="O8" t="n">
-        <v>13.22983849996524</v>
+        <v>13.21922204681576</v>
       </c>
       <c r="P8" t="n">
-        <v>339.4327731879546</v>
+        <v>339.4337337078335</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -39320,28 +39381,28 @@
         <v>0.0912</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.002610530137179982</v>
+        <v>-0.003024169853293514</v>
       </c>
       <c r="J9" t="n">
+        <v>625</v>
+      </c>
+      <c r="K9" t="n">
         <v>624</v>
       </c>
-      <c r="K9" t="n">
-        <v>623</v>
-      </c>
       <c r="L9" t="n">
-        <v>4.644720958402182e-06</v>
+        <v>6.254673511563169e-06</v>
       </c>
       <c r="M9" t="n">
-        <v>7.27890396974962</v>
+        <v>7.269367896607541</v>
       </c>
       <c r="N9" t="n">
-        <v>83.2278565555937</v>
+        <v>83.09727886088487</v>
       </c>
       <c r="O9" t="n">
-        <v>9.122930261467184</v>
+        <v>9.115770886813955</v>
       </c>
       <c r="P9" t="n">
-        <v>345.2956769942793</v>
+        <v>345.2998386994796</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39398,28 +39459,28 @@
         <v>0.1192</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08024095961186097</v>
+        <v>0.08189072965700413</v>
       </c>
       <c r="J10" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K10" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003879156029939157</v>
+        <v>0.004051716701114816</v>
       </c>
       <c r="M10" t="n">
-        <v>7.862955250104946</v>
+        <v>7.859269592721721</v>
       </c>
       <c r="N10" t="n">
-        <v>93.653477888734</v>
+        <v>93.54809009076865</v>
       </c>
       <c r="O10" t="n">
-        <v>9.677472701523575</v>
+        <v>9.67202616263876</v>
       </c>
       <c r="P10" t="n">
-        <v>350.0466541565373</v>
+        <v>350.0300472045685</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39476,28 +39537,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1576489098499047</v>
+        <v>-0.1582028440532159</v>
       </c>
       <c r="J11" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K11" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L11" t="n">
-        <v>0.007467420016533</v>
+        <v>0.007545321034139074</v>
       </c>
       <c r="M11" t="n">
-        <v>10.81914456596447</v>
+        <v>10.80467087064595</v>
       </c>
       <c r="N11" t="n">
-        <v>187.1169106135892</v>
+        <v>186.82253562719</v>
       </c>
       <c r="O11" t="n">
-        <v>13.67906833865484</v>
+        <v>13.66830405087588</v>
       </c>
       <c r="P11" t="n">
-        <v>366.4607967190175</v>
+        <v>366.4663727438311</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39554,28 +39615,28 @@
         <v>0.0789</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9306741826960082</v>
+        <v>-0.9347535737326831</v>
       </c>
       <c r="J12" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K12" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05102844378053817</v>
+        <v>0.05160912939954165</v>
       </c>
       <c r="M12" t="n">
-        <v>25.41467984873916</v>
+        <v>25.39482609483838</v>
       </c>
       <c r="N12" t="n">
-        <v>917.4972927464127</v>
+        <v>916.2804464144109</v>
       </c>
       <c r="O12" t="n">
-        <v>30.29021777317576</v>
+        <v>30.27012465145149</v>
       </c>
       <c r="P12" t="n">
-        <v>349.9812734117081</v>
+        <v>350.0222969716678</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -39632,28 +39693,28 @@
         <v>0.1373</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.02407588778117379</v>
+        <v>-0.03069039461461451</v>
       </c>
       <c r="J13" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K13" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="L13" t="n">
-        <v>2.814323809408048e-05</v>
+        <v>4.586132137296417e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>28.58002651367707</v>
+        <v>28.57081272420865</v>
       </c>
       <c r="N13" t="n">
-        <v>1166.635630107664</v>
+        <v>1165.483666975103</v>
       </c>
       <c r="O13" t="n">
-        <v>34.1560482214741</v>
+        <v>34.13918081874699</v>
       </c>
       <c r="P13" t="n">
-        <v>318.1833504845781</v>
+        <v>318.2499335805703</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -39710,28 +39771,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.53009599161585</v>
+        <v>-1.539191030969835</v>
       </c>
       <c r="J14" t="n">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K14" t="n">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06871662491862496</v>
+        <v>0.06965409149689128</v>
       </c>
       <c r="M14" t="n">
-        <v>35.15082934028405</v>
+        <v>35.15130963367854</v>
       </c>
       <c r="N14" t="n">
-        <v>1805.634063079129</v>
+        <v>1804.063847969957</v>
       </c>
       <c r="O14" t="n">
-        <v>42.49275306542433</v>
+        <v>42.47427277741147</v>
       </c>
       <c r="P14" t="n">
-        <v>348.9052644682116</v>
+        <v>348.9969372512874</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -39769,7 +39830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O625"/>
+  <dimension ref="A1:O626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87769,6 +87830,83 @@
         </is>
       </c>
     </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>-37.2081305708302,174.61379249189892</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>-37.207379300374335,174.61370314708262</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>-37.20686382726254,174.61294772881203</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>-37.206238233438064,174.61250335253374</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>-37.20555095773044,174.61223319411118</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>-37.204894897326945,174.611874845052</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>-37.204151747229574,174.61176829007974</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>-37.20353020514482,174.61131465682723</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>-37.20291530450549,174.61083447304796</t>
+        </is>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>-37.202263783243836,174.61046251704772</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr">
+        <is>
+          <t>-37.20143359039563,174.61062127950902</t>
+        </is>
+      </c>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>-37.200714591103534,174.61044972656595</t>
+        </is>
+      </c>
+      <c r="N626" t="inlineStr">
+        <is>
+          <t>-37.19999390848344,174.61028315496165</t>
+        </is>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0196/nzd0196.xlsx
+++ b/data/nzd0196/nzd0196.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O626"/>
+  <dimension ref="A1:O630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32314,6 +32314,210 @@
         <v>279.69</v>
       </c>
       <c r="O626" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:33+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>343.46</v>
+      </c>
+      <c r="C627" t="n">
+        <v>321.63</v>
+      </c>
+      <c r="D627" t="n">
+        <v>356.2</v>
+      </c>
+      <c r="E627" t="n">
+        <v>365.53</v>
+      </c>
+      <c r="F627" t="n">
+        <v>356.61</v>
+      </c>
+      <c r="G627" t="n">
+        <v>356.49</v>
+      </c>
+      <c r="H627" t="n">
+        <v>333.49</v>
+      </c>
+      <c r="I627" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="J627" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="K627" t="n">
+        <v>363.68</v>
+      </c>
+      <c r="L627" t="n">
+        <v>312.55</v>
+      </c>
+      <c r="M627" t="n">
+        <v>299.78</v>
+      </c>
+      <c r="N627" t="n">
+        <v>288.06</v>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>343.6</v>
+      </c>
+      <c r="C628" t="n">
+        <v>323.13</v>
+      </c>
+      <c r="D628" t="n">
+        <v>356.22</v>
+      </c>
+      <c r="E628" t="n">
+        <v>365.32</v>
+      </c>
+      <c r="F628" t="n">
+        <v>356.63</v>
+      </c>
+      <c r="G628" t="n">
+        <v>356.61</v>
+      </c>
+      <c r="H628" t="n">
+        <v>334.08</v>
+      </c>
+      <c r="I628" t="n">
+        <v>343.61</v>
+      </c>
+      <c r="J628" t="n">
+        <v>357.08</v>
+      </c>
+      <c r="K628" t="n">
+        <v>363.93</v>
+      </c>
+      <c r="L628" t="n">
+        <v>317.19</v>
+      </c>
+      <c r="M628" t="n">
+        <v>305.2</v>
+      </c>
+      <c r="N628" t="n">
+        <v>293</v>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:12:28+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>344.14</v>
+      </c>
+      <c r="C629" t="n">
+        <v>326.34</v>
+      </c>
+      <c r="D629" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="E629" t="n">
+        <v>366.47</v>
+      </c>
+      <c r="F629" t="n">
+        <v>355.79</v>
+      </c>
+      <c r="G629" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="H629" t="n">
+        <v>332.06</v>
+      </c>
+      <c r="I629" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="J629" t="n">
+        <v>357.57</v>
+      </c>
+      <c r="K629" t="n">
+        <v>368.11</v>
+      </c>
+      <c r="L629" t="n">
+        <v>327.54</v>
+      </c>
+      <c r="M629" t="n">
+        <v>314.82</v>
+      </c>
+      <c r="N629" t="n">
+        <v>306.38</v>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>343.92</v>
+      </c>
+      <c r="C630" t="n">
+        <v>327</v>
+      </c>
+      <c r="D630" t="n">
+        <v>356.8</v>
+      </c>
+      <c r="E630" t="n">
+        <v>366.47</v>
+      </c>
+      <c r="F630" t="n">
+        <v>354.95</v>
+      </c>
+      <c r="G630" t="n">
+        <v>354.9</v>
+      </c>
+      <c r="H630" t="n">
+        <v>330.22</v>
+      </c>
+      <c r="I630" t="n">
+        <v>342.52</v>
+      </c>
+      <c r="J630" t="n">
+        <v>357.43</v>
+      </c>
+      <c r="K630" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="L630" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="M630" t="n">
+        <v>317.75</v>
+      </c>
+      <c r="N630" t="n">
+        <v>309.45</v>
+      </c>
+      <c r="O630" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32330,7 +32534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B633"/>
+  <dimension ref="A1:B637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38663,6 +38867,46 @@
       </c>
       <c r="B633" t="n">
         <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>0.27</v>
       </c>
     </row>
   </sheetData>
@@ -38831,28 +39075,28 @@
         <v>0.0824</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1586531750820686</v>
+        <v>-0.169723911278183</v>
       </c>
       <c r="J2" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K2" t="n">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01570819127579381</v>
+        <v>0.01807792001424724</v>
       </c>
       <c r="M2" t="n">
-        <v>7.702435746899327</v>
+        <v>7.705711451183986</v>
       </c>
       <c r="N2" t="n">
-        <v>89.77772140282583</v>
+        <v>89.71453304565186</v>
       </c>
       <c r="O2" t="n">
-        <v>9.475110627471631</v>
+        <v>9.471775601525401</v>
       </c>
       <c r="P2" t="n">
-        <v>356.9736803432426</v>
+        <v>357.085145628827</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38909,28 +39153,28 @@
         <v>0.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09031578113841657</v>
+        <v>0.06926437822759711</v>
       </c>
       <c r="J3" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K3" t="n">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001049095526386101</v>
+        <v>0.0006231806984789978</v>
       </c>
       <c r="M3" t="n">
-        <v>17.67042790193748</v>
+        <v>17.66985263376633</v>
       </c>
       <c r="N3" t="n">
-        <v>438.1380738769571</v>
+        <v>437.1911615087897</v>
       </c>
       <c r="O3" t="n">
-        <v>20.93174798904662</v>
+        <v>20.9091167080006</v>
       </c>
       <c r="P3" t="n">
-        <v>339.2047704895372</v>
+        <v>339.4182333432742</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38987,28 +39231,28 @@
         <v>0.0453</v>
       </c>
       <c r="I4" t="n">
-        <v>0.210946375346973</v>
+        <v>0.2040828378429679</v>
       </c>
       <c r="J4" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K4" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02676863526269913</v>
+        <v>0.02538300626798107</v>
       </c>
       <c r="M4" t="n">
-        <v>7.857479121526288</v>
+        <v>7.844784923019801</v>
       </c>
       <c r="N4" t="n">
-        <v>91.81248224018516</v>
+        <v>91.42409384121548</v>
       </c>
       <c r="O4" t="n">
-        <v>9.58188302162916</v>
+        <v>9.561594733161172</v>
       </c>
       <c r="P4" t="n">
-        <v>356.5486379795953</v>
+        <v>356.6178257636495</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39065,28 +39309,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1931644834464704</v>
+        <v>0.1951423992292569</v>
       </c>
       <c r="J5" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K5" t="n">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02856251433430168</v>
+        <v>0.02951635164631938</v>
       </c>
       <c r="M5" t="n">
-        <v>6.880600401832926</v>
+        <v>6.845869649860222</v>
       </c>
       <c r="N5" t="n">
-        <v>72.2224879116404</v>
+        <v>71.77972633879774</v>
       </c>
       <c r="O5" t="n">
-        <v>8.49838148776815</v>
+        <v>8.472291681640673</v>
       </c>
       <c r="P5" t="n">
-        <v>359.2548310100523</v>
+        <v>359.2349088707293</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39143,28 +39387,28 @@
         <v>0.0466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04661116353248974</v>
+        <v>0.0436091274408324</v>
       </c>
       <c r="J6" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K6" t="n">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001376287712573365</v>
+        <v>0.00122097688142131</v>
       </c>
       <c r="M6" t="n">
-        <v>7.548093837030768</v>
+        <v>7.515117666018598</v>
       </c>
       <c r="N6" t="n">
-        <v>89.7164329646377</v>
+        <v>89.18457292847999</v>
       </c>
       <c r="O6" t="n">
-        <v>9.471875894702046</v>
+        <v>9.443758411166606</v>
       </c>
       <c r="P6" t="n">
-        <v>357.2160648821587</v>
+        <v>357.2463014824421</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39221,28 +39465,28 @@
         <v>0.0487</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01655121824314089</v>
+        <v>-0.0208304809973149</v>
       </c>
       <c r="J7" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K7" t="n">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0002618911351297548</v>
+        <v>0.0004199178027840533</v>
       </c>
       <c r="M7" t="n">
-        <v>6.169699489249738</v>
+        <v>6.150034416744634</v>
       </c>
       <c r="N7" t="n">
-        <v>59.51478211530231</v>
+        <v>59.21406475066362</v>
       </c>
       <c r="O7" t="n">
-        <v>7.714582432983804</v>
+        <v>7.695067559850506</v>
       </c>
       <c r="P7" t="n">
-        <v>359.8730574360607</v>
+        <v>359.9161563257838</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39299,28 +39543,28 @@
         <v>0.0425</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2330088868071059</v>
+        <v>-0.2340486195858938</v>
       </c>
       <c r="J8" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K8" t="n">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01737482856475814</v>
+        <v>0.01776325736225992</v>
       </c>
       <c r="M8" t="n">
-        <v>10.59371895193605</v>
+        <v>10.53460614798571</v>
       </c>
       <c r="N8" t="n">
-        <v>174.7478315230197</v>
+        <v>173.6515670732506</v>
       </c>
       <c r="O8" t="n">
-        <v>13.21922204681576</v>
+        <v>13.17769202376693</v>
       </c>
       <c r="P8" t="n">
-        <v>339.4337337078335</v>
+        <v>339.4442131010299</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -39381,28 +39625,28 @@
         <v>0.0912</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.003024169853293514</v>
+        <v>-0.005803129349723563</v>
       </c>
       <c r="J9" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K9" t="n">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="L9" t="n">
-        <v>6.254673511563169e-06</v>
+        <v>2.333914411223326e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>7.269367896607541</v>
+        <v>7.237234933432062</v>
       </c>
       <c r="N9" t="n">
-        <v>83.09727886088487</v>
+        <v>82.6023706176119</v>
       </c>
       <c r="O9" t="n">
-        <v>9.115770886813955</v>
+        <v>9.088584632252257</v>
       </c>
       <c r="P9" t="n">
-        <v>345.2998386994796</v>
+        <v>345.3278424962357</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39459,28 +39703,28 @@
         <v>0.1192</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08189072965700413</v>
+        <v>0.08821047794984627</v>
       </c>
       <c r="J10" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K10" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004051716701114816</v>
+        <v>0.004754346153326483</v>
       </c>
       <c r="M10" t="n">
-        <v>7.859269592721721</v>
+        <v>7.843133526565755</v>
       </c>
       <c r="N10" t="n">
-        <v>93.54809009076865</v>
+        <v>93.11863779302078</v>
       </c>
       <c r="O10" t="n">
-        <v>9.67202616263876</v>
+        <v>9.649799883573793</v>
       </c>
       <c r="P10" t="n">
-        <v>350.0300472045685</v>
+        <v>349.9663384041817</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39537,28 +39781,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1582028440532159</v>
+        <v>-0.153839733238181</v>
       </c>
       <c r="J11" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K11" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="L11" t="n">
-        <v>0.007545321034139074</v>
+        <v>0.007231621236120311</v>
       </c>
       <c r="M11" t="n">
-        <v>10.80467087064595</v>
+        <v>10.75812920429735</v>
       </c>
       <c r="N11" t="n">
-        <v>186.82253562719</v>
+        <v>185.7402702878714</v>
       </c>
       <c r="O11" t="n">
-        <v>13.66830405087588</v>
+        <v>13.62865621724576</v>
       </c>
       <c r="P11" t="n">
-        <v>366.4663727438311</v>
+        <v>366.4223763275214</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39615,28 +39859,28 @@
         <v>0.0789</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9347535737326831</v>
+        <v>-0.9392789813378664</v>
       </c>
       <c r="J12" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K12" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05160912939954165</v>
+        <v>0.05274463510455751</v>
       </c>
       <c r="M12" t="n">
-        <v>25.39482609483838</v>
+        <v>25.27592664310509</v>
       </c>
       <c r="N12" t="n">
-        <v>916.2804464144109</v>
+        <v>910.7840273121415</v>
       </c>
       <c r="O12" t="n">
-        <v>30.27012465145149</v>
+        <v>30.17919858631341</v>
       </c>
       <c r="P12" t="n">
-        <v>350.0222969716678</v>
+        <v>350.067826560423</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -39693,28 +39937,28 @@
         <v>0.1373</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03069039461461451</v>
+        <v>-0.04056892997852451</v>
       </c>
       <c r="J13" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K13" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="L13" t="n">
-        <v>4.586132137296417e-05</v>
+        <v>8.118891345543222e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>28.57081272420865</v>
+        <v>28.44478342034486</v>
       </c>
       <c r="N13" t="n">
-        <v>1165.483666975103</v>
+        <v>1158.809076632846</v>
       </c>
       <c r="O13" t="n">
-        <v>34.13918081874699</v>
+        <v>34.04128488516328</v>
       </c>
       <c r="P13" t="n">
-        <v>318.2499335805703</v>
+        <v>318.3494714935675</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -39771,28 +40015,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.539191030969835</v>
+        <v>-1.5506346444494</v>
       </c>
       <c r="J14" t="n">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K14" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06965409149689128</v>
+        <v>0.0714844045562012</v>
       </c>
       <c r="M14" t="n">
-        <v>35.15130963367854</v>
+        <v>34.99998300215172</v>
       </c>
       <c r="N14" t="n">
-        <v>1804.063847969957</v>
+        <v>1793.488203991079</v>
       </c>
       <c r="O14" t="n">
-        <v>42.47427277741147</v>
+        <v>42.34959508650678</v>
       </c>
       <c r="P14" t="n">
-        <v>348.9969372512874</v>
+        <v>349.1123937534213</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -39830,7 +40074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O626"/>
+  <dimension ref="A1:O630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87907,6 +88151,314 @@
         </is>
       </c>
     </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:33+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>-37.208131883892996,174.61378878286894</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>-37.207394984178755,174.61365884521126</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>-37.20686379078909,174.61294783183925</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>-37.20624053124595,174.612496861861</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>-37.20555070241942,174.61223391529109</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>-37.20489296426895,174.61188030537394</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>-37.20415346641008,174.6117633276808</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>-37.20352880284758,174.61131880835543</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>-37.20291467527373,174.61083634217056</t>
+        </is>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>-37.20227472480719,174.61043001531354</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr">
+        <is>
+          <t>-37.20143359039563,174.61062127950902</t>
+        </is>
+      </c>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>-37.20072654647679,174.61041421424198</t>
+        </is>
+      </c>
+      <c r="N627" t="inlineStr">
+        <is>
+          <t>-37.2000231676207,174.61019624399557</t>
+        </is>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>-37.2081323945285,174.61378734046832</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>-37.20740045526953,174.6136433910656</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>-37.20686386373596,174.61294762578478</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>-37.20623976531004,174.61249902541863</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>-37.20555077536543,174.61223370923972</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>-37.204893401942485,174.61187906907466</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>-37.20415557956916,174.61175722806513</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>-37.20352918847933,174.6113176666852</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>-37.20291404604197,174.61083821129313</t>
+        </is>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>-37.20227559873361,174.61042741932795</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr">
+        <is>
+          <t>-37.201449810576825,174.61057309860493</t>
+        </is>
+      </c>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>-37.20074549327508,174.61035793445342</t>
+        </is>
+      </c>
+      <c r="N628" t="inlineStr">
+        <is>
+          <t>-37.20004043642513,174.61014494884105</t>
+        </is>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:12:28+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>-37.20813436412244,174.61378177692296</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>-37.20741216339716,174.6136103191863</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>-37.206865979194816,174.6129416502058</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>-37.20624395972056,174.61248717736441</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>-37.205547711632704,174.6122423633984</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>-37.204890447645894,174.61188741409458</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>-37.204148344684214,174.6117781114936</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>-37.20352424538054,174.61133230082095</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>-37.202915758950596,174.61083312312604</t>
+        </is>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>-37.20229021077497,174.61038401444003</t>
+        </is>
+      </c>
+      <c r="L629" t="inlineStr">
+        <is>
+          <t>-37.201485991299954,174.6104656260376</t>
+        </is>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>-37.20077912202979,174.6102580429493</t>
+        </is>
+      </c>
+      <c r="N629" t="inlineStr">
+        <is>
+          <t>-37.20008720890785,174.6100060156903</t>
+        </is>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>-37.2081335616953,174.61378404355258</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>-37.2074145706746,174.61360351935934</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>-37.206865979194816,174.6129416502058</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>-37.20624395972056,174.61248717736441</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>-37.20554464789938,174.61225101755633</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>-37.20488716509347,174.61189668633816</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>-37.20414175448887,174.61179713401893</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>-37.20352536721873,174.61132897959882</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>-37.20291526954815,174.61083457688812</t>
+        </is>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>-37.20228884745119,174.6103880641791</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr">
+        <is>
+          <t>-37.20149389161907,174.61044215858374</t>
+        </is>
+      </c>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>-37.200789364451204,174.6102276185957</t>
+        </is>
+      </c>
+      <c r="N630" t="inlineStr">
+        <is>
+          <t>-37.20009794068821,174.60997413787968</t>
+        </is>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0196/nzd0196.xlsx
+++ b/data/nzd0196/nzd0196.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O630"/>
+  <dimension ref="A1:O633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32485,10 +32485,10 @@
         <v>327</v>
       </c>
       <c r="D630" t="n">
-        <v>356.8</v>
+        <v>355.84</v>
       </c>
       <c r="E630" t="n">
-        <v>366.47</v>
+        <v>365.28</v>
       </c>
       <c r="F630" t="n">
         <v>354.95</v>
@@ -32497,7 +32497,7 @@
         <v>354.9</v>
       </c>
       <c r="H630" t="n">
-        <v>330.22</v>
+        <v>332.06</v>
       </c>
       <c r="I630" t="n">
         <v>342.52</v>
@@ -32520,6 +32520,159 @@
       <c r="O630" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>343.78</v>
+      </c>
+      <c r="C631" t="n">
+        <v>328.05</v>
+      </c>
+      <c r="D631" t="n">
+        <v>355.42</v>
+      </c>
+      <c r="E631" t="n">
+        <v>365.05</v>
+      </c>
+      <c r="F631" t="n">
+        <v>355.47</v>
+      </c>
+      <c r="G631" t="n">
+        <v>355.39</v>
+      </c>
+      <c r="H631" t="n">
+        <v>333.26</v>
+      </c>
+      <c r="I631" t="n">
+        <v>343.5</v>
+      </c>
+      <c r="J631" t="n">
+        <v>357.64</v>
+      </c>
+      <c r="K631" t="n">
+        <v>367.96</v>
+      </c>
+      <c r="L631" t="n">
+        <v>332.79</v>
+      </c>
+      <c r="M631" t="n">
+        <v>321.24</v>
+      </c>
+      <c r="N631" t="n">
+        <v>312.73</v>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:30+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>343.78</v>
+      </c>
+      <c r="C632" t="n">
+        <v>332.3</v>
+      </c>
+      <c r="D632" t="n">
+        <v>354.12</v>
+      </c>
+      <c r="E632" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="F632" t="n">
+        <v>355.51</v>
+      </c>
+      <c r="G632" t="n">
+        <v>355.17</v>
+      </c>
+      <c r="H632" t="n">
+        <v>334.68</v>
+      </c>
+      <c r="I632" t="n">
+        <v>344.05</v>
+      </c>
+      <c r="J632" t="n">
+        <v>357.22</v>
+      </c>
+      <c r="K632" t="n">
+        <v>371.62</v>
+      </c>
+      <c r="L632" t="n">
+        <v>343.17</v>
+      </c>
+      <c r="M632" t="n">
+        <v>324.52</v>
+      </c>
+      <c r="N632" t="n">
+        <v>324.1</v>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>345.28</v>
+      </c>
+      <c r="C633" t="n">
+        <v>333.81</v>
+      </c>
+      <c r="D633" t="n">
+        <v>354.4</v>
+      </c>
+      <c r="E633" t="n">
+        <v>364.53</v>
+      </c>
+      <c r="F633" t="n">
+        <v>355.51</v>
+      </c>
+      <c r="G633" t="n">
+        <v>356.62</v>
+      </c>
+      <c r="H633" t="n">
+        <v>336.9</v>
+      </c>
+      <c r="I633" t="n">
+        <v>342.67</v>
+      </c>
+      <c r="J633" t="n">
+        <v>358.46</v>
+      </c>
+      <c r="K633" t="n">
+        <v>372.66</v>
+      </c>
+      <c r="L633" t="n">
+        <v>346.49</v>
+      </c>
+      <c r="M633" t="n">
+        <v>328.32</v>
+      </c>
+      <c r="N633" t="n">
+        <v>327.32</v>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -32534,7 +32687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B637"/>
+  <dimension ref="A1:B640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38907,6 +39060,36 @@
       </c>
       <c r="B637" t="n">
         <v>0.27</v>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -39075,28 +39258,28 @@
         <v>0.0824</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.169723911278183</v>
+        <v>-0.1773165455006624</v>
       </c>
       <c r="J2" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K2" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01807792001424724</v>
+        <v>0.01982482194141899</v>
       </c>
       <c r="M2" t="n">
-        <v>7.705711451183986</v>
+        <v>7.705288710604838</v>
       </c>
       <c r="N2" t="n">
-        <v>89.71453304565186</v>
+        <v>89.61515322982908</v>
       </c>
       <c r="O2" t="n">
-        <v>9.471775601525401</v>
+        <v>9.466528045161493</v>
       </c>
       <c r="P2" t="n">
-        <v>357.085145628827</v>
+        <v>357.1618120172773</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39153,28 +39336,28 @@
         <v>0.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06926437822759711</v>
+        <v>0.0602248610275824</v>
       </c>
       <c r="J3" t="n">
+        <v>632</v>
+      </c>
+      <c r="K3" t="n">
         <v>629</v>
       </c>
-      <c r="K3" t="n">
-        <v>626</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0006231806984789978</v>
+        <v>0.0004754971005251907</v>
       </c>
       <c r="M3" t="n">
-        <v>17.66985263376633</v>
+        <v>17.63336283640732</v>
       </c>
       <c r="N3" t="n">
-        <v>437.1911615087897</v>
+        <v>435.5909270969597</v>
       </c>
       <c r="O3" t="n">
-        <v>20.9091167080006</v>
+        <v>20.87081519962648</v>
       </c>
       <c r="P3" t="n">
-        <v>339.4182333432742</v>
+        <v>339.5101448965104</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39231,28 +39414,28 @@
         <v>0.0453</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2040828378429679</v>
+        <v>0.1970886642382823</v>
       </c>
       <c r="J4" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K4" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02538300626798107</v>
+        <v>0.02388075609811069</v>
       </c>
       <c r="M4" t="n">
-        <v>7.844784923019801</v>
+        <v>7.84568454314733</v>
       </c>
       <c r="N4" t="n">
-        <v>91.42409384121548</v>
+        <v>91.2611308821983</v>
       </c>
       <c r="O4" t="n">
-        <v>9.561594733161172</v>
+        <v>9.553069186507459</v>
       </c>
       <c r="P4" t="n">
-        <v>356.6178257636495</v>
+        <v>356.6885343126486</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39309,28 +39492,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1951423992292569</v>
+        <v>0.1950783094905881</v>
       </c>
       <c r="J5" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K5" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02951635164631938</v>
+        <v>0.02979175210411455</v>
       </c>
       <c r="M5" t="n">
-        <v>6.845869649860222</v>
+        <v>6.812969240023715</v>
       </c>
       <c r="N5" t="n">
-        <v>71.77972633879774</v>
+        <v>71.43305935293994</v>
       </c>
       <c r="O5" t="n">
-        <v>8.472291681640673</v>
+        <v>8.451808052300995</v>
       </c>
       <c r="P5" t="n">
-        <v>359.2349088707293</v>
+        <v>359.2355498055093</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39387,28 +39570,28 @@
         <v>0.0466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0436091274408324</v>
+        <v>0.04096789099221</v>
       </c>
       <c r="J6" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K6" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00122097688142131</v>
+        <v>0.001088221622628782</v>
       </c>
       <c r="M6" t="n">
-        <v>7.515117666018598</v>
+        <v>7.492580523872719</v>
       </c>
       <c r="N6" t="n">
-        <v>89.18457292847999</v>
+        <v>88.79926366489785</v>
       </c>
       <c r="O6" t="n">
-        <v>9.443758411166606</v>
+        <v>9.423336121825319</v>
       </c>
       <c r="P6" t="n">
-        <v>357.2463014824421</v>
+        <v>357.2729776932466</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39465,28 +39648,28 @@
         <v>0.0487</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0208304809973149</v>
+        <v>-0.02414794650542968</v>
       </c>
       <c r="J7" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K7" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0004199178027840533</v>
+        <v>0.0005693793300205474</v>
       </c>
       <c r="M7" t="n">
-        <v>6.150034416744634</v>
+        <v>6.136072740389196</v>
       </c>
       <c r="N7" t="n">
-        <v>59.21406475066362</v>
+        <v>58.99615818440613</v>
       </c>
       <c r="O7" t="n">
-        <v>7.695067559850506</v>
+        <v>7.680895662903261</v>
       </c>
       <c r="P7" t="n">
-        <v>359.9161563257838</v>
+        <v>359.9496602830727</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39543,28 +39726,28 @@
         <v>0.0425</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2340486195858938</v>
+        <v>-0.231968574391541</v>
       </c>
       <c r="J8" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K8" t="n">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01776325736225992</v>
+        <v>0.01762839784892511</v>
       </c>
       <c r="M8" t="n">
-        <v>10.53460614798571</v>
+        <v>10.48942029456206</v>
       </c>
       <c r="N8" t="n">
-        <v>173.6515670732506</v>
+        <v>172.8357705423986</v>
       </c>
       <c r="O8" t="n">
-        <v>13.17769202376693</v>
+        <v>13.14670188839766</v>
       </c>
       <c r="P8" t="n">
-        <v>339.4442131010299</v>
+        <v>339.4232072086178</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -39625,28 +39808,28 @@
         <v>0.0912</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.005803129349723563</v>
+        <v>-0.007416676746140558</v>
       </c>
       <c r="J9" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K9" t="n">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="L9" t="n">
-        <v>2.333914411223326e-05</v>
+        <v>3.850365444024728e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>7.237234933432062</v>
+        <v>7.210971425259382</v>
       </c>
       <c r="N9" t="n">
-        <v>82.6023706176119</v>
+        <v>82.22583320078002</v>
       </c>
       <c r="O9" t="n">
-        <v>9.088584632252257</v>
+        <v>9.067846116955229</v>
       </c>
       <c r="P9" t="n">
-        <v>345.3278424962357</v>
+        <v>345.3441482153308</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39703,28 +39886,28 @@
         <v>0.1192</v>
       </c>
       <c r="I10" t="n">
-        <v>0.08821047794984627</v>
+        <v>0.09321099523426597</v>
       </c>
       <c r="J10" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K10" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="L10" t="n">
-        <v>0.004754346153326483</v>
+        <v>0.005351522790047469</v>
       </c>
       <c r="M10" t="n">
-        <v>7.843133526565755</v>
+        <v>7.832524148546055</v>
       </c>
       <c r="N10" t="n">
-        <v>93.11863779302078</v>
+        <v>92.8184442979901</v>
       </c>
       <c r="O10" t="n">
-        <v>9.649799883573793</v>
+        <v>9.634232937706566</v>
       </c>
       <c r="P10" t="n">
-        <v>349.9663384041817</v>
+        <v>349.9157824361218</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39781,28 +39964,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.153839733238181</v>
+        <v>-0.1461948828060484</v>
       </c>
       <c r="J11" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K11" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="L11" t="n">
-        <v>0.007231621236120311</v>
+        <v>0.006589392677902373</v>
       </c>
       <c r="M11" t="n">
-        <v>10.75812920429735</v>
+        <v>10.74556822165851</v>
       </c>
       <c r="N11" t="n">
-        <v>185.7402702878714</v>
+        <v>185.206190586349</v>
       </c>
       <c r="O11" t="n">
-        <v>13.62865621724576</v>
+        <v>13.60904811463127</v>
       </c>
       <c r="P11" t="n">
-        <v>366.4223763275214</v>
+        <v>366.345070159595</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -39859,28 +40042,28 @@
         <v>0.0789</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9392789813378664</v>
+        <v>-0.9250461163885412</v>
       </c>
       <c r="J12" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K12" t="n">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05274463510455751</v>
+        <v>0.05166692753538615</v>
       </c>
       <c r="M12" t="n">
-        <v>25.27592664310509</v>
+        <v>25.22673156268298</v>
       </c>
       <c r="N12" t="n">
-        <v>910.7840273121415</v>
+        <v>907.7039558815716</v>
       </c>
       <c r="O12" t="n">
-        <v>30.17919858631341</v>
+        <v>30.12812566160682</v>
       </c>
       <c r="P12" t="n">
-        <v>350.067826560423</v>
+        <v>349.9240164484032</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -39937,28 +40120,28 @@
         <v>0.1373</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.04056892997852451</v>
+        <v>-0.03380626923308989</v>
       </c>
       <c r="J13" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K13" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="L13" t="n">
-        <v>8.118891345543222e-05</v>
+        <v>5.694038541204094e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>28.44478342034486</v>
+        <v>28.34205506395368</v>
       </c>
       <c r="N13" t="n">
-        <v>1158.809076632846</v>
+        <v>1153.604952519378</v>
       </c>
       <c r="O13" t="n">
-        <v>34.04128488516328</v>
+        <v>33.96476045137633</v>
       </c>
       <c r="P13" t="n">
-        <v>318.3494714935675</v>
+        <v>318.2810796138564</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -40015,28 +40198,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.5506346444494</v>
+        <v>-1.538593693637934</v>
       </c>
       <c r="J14" t="n">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K14" t="n">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0714844045562012</v>
+        <v>0.0710862991719976</v>
       </c>
       <c r="M14" t="n">
-        <v>34.99998300215172</v>
+        <v>34.8808544925338</v>
       </c>
       <c r="N14" t="n">
-        <v>1793.488203991079</v>
+        <v>1785.862056785139</v>
       </c>
       <c r="O14" t="n">
-        <v>42.34959508650678</v>
+        <v>42.25946115114507</v>
       </c>
       <c r="P14" t="n">
-        <v>349.1123937534213</v>
+        <v>348.9904376411809</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -40074,7 +40257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O630"/>
+  <dimension ref="A1:O633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88400,12 +88583,12 @@
       </c>
       <c r="D630" t="inlineStr">
         <is>
-          <t>-37.206865979194816,174.6129416502058</t>
+          <t>-37.20686247774552,174.61295154081913</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>-37.20624395972056,174.61248717736441</t>
+          <t>-37.20623961941747,174.61249943752483</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
@@ -88420,7 +88603,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t>-37.20414175448887,174.61179713401893</t>
+          <t>-37.204148344684214,174.6117781114936</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -88456,6 +88639,237 @@
       <c r="O630" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>-37.208133051059825,174.61378548595323</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>-37.20741840043342,174.6135927014519</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>-37.206860945861195,174.61295586796217</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>-37.20623878053522,174.6125018071355</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>-37.20554654449627,174.61224566022054</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>-37.20488895226099,174.61189163811676</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>-37.204152642636096,174.611765705497</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>-37.20352880284758,174.61131880835543</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>-37.202916003651815,174.61083239624503</t>
+        </is>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>-37.20228968641969,174.610385572032</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr">
+        <is>
+          <t>-37.20150434380421,174.6104111109269</t>
+        </is>
+      </c>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>-37.20080156445856,174.61019137933758</t>
+        </is>
+      </c>
+      <c r="N631" t="inlineStr">
+        <is>
+          <t>-37.20010940655503,174.60994007949196</t>
+        </is>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-08 22:12:30+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>-37.208133051059825,174.61378548595323</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>-37.20743390182826,174.61354891467224</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>-37.206856204313524,174.61296926149896</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>-37.206236883931695,174.61250716451593</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>-37.20554669038834,174.61224524811777</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>-37.20488814985927,174.61189390466518</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>-37.20415772854419,174.6117510250658</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>-37.20353073100626,174.6113131000041</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>-37.20291453544445,174.61083675753113</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>-37.20230248068285,174.6103475667816</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>-37.20154062925474,174.61030332668508</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>-37.20081303035814,174.61015732065422</t>
+        </is>
+      </c>
+      <c r="N632" t="inlineStr">
+        <is>
+          <t>-37.200149152488784,174.60982201725486</t>
+        </is>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>-37.20813852215322,174.61377003165958</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>-37.207439409378864,174.61353335748254</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>-37.206857225570076,174.61296637673735</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>-37.206236883931695,174.61250716451593</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>-37.20554669038834,174.61224524811777</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>-37.204893438415276,174.61187896604972</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>-37.204165679749046,174.61172807396505</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>-37.20352589308035,174.61132742277593</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>-37.20291887015145,174.61082388135262</t>
+        </is>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>-37.20230611620901,174.61033676747306</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr">
+        <is>
+          <t>-37.201552234985535,174.61026885231942</t>
+        </is>
+      </c>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>-37.20082631401034,174.61011786241022</t>
+        </is>
+      </c>
+      <c r="N633" t="inlineStr">
+        <is>
+          <t>-37.200160408572245,174.60978858184</t>
+        </is>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>

--- a/data/nzd0196/nzd0196.xlsx
+++ b/data/nzd0196/nzd0196.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O633"/>
+  <dimension ref="A1:O634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32644,7 +32644,7 @@
         <v>364.53</v>
       </c>
       <c r="F633" t="n">
-        <v>355.51</v>
+        <v>357.97</v>
       </c>
       <c r="G633" t="n">
         <v>356.62</v>
@@ -32671,6 +32671,57 @@
         <v>327.32</v>
       </c>
       <c r="O633" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="C634" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="D634" t="n">
+        <v>353.53</v>
+      </c>
+      <c r="E634" t="n">
+        <v>363.78</v>
+      </c>
+      <c r="F634" t="n">
+        <v>358.48</v>
+      </c>
+      <c r="G634" t="n">
+        <v>357.29</v>
+      </c>
+      <c r="H634" t="n">
+        <v>338.94</v>
+      </c>
+      <c r="I634" t="n">
+        <v>341.56</v>
+      </c>
+      <c r="J634" t="n">
+        <v>356.47</v>
+      </c>
+      <c r="K634" t="n">
+        <v>369.76</v>
+      </c>
+      <c r="L634" t="n">
+        <v>349.74</v>
+      </c>
+      <c r="M634" t="n">
+        <v>345.94</v>
+      </c>
+      <c r="N634" t="n">
+        <v>343.26</v>
+      </c>
+      <c r="O634" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -32687,7 +32738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B640"/>
+  <dimension ref="A1:B641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39090,6 +39141,16 @@
       </c>
       <c r="B640" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>-0.47</v>
       </c>
     </row>
   </sheetData>
@@ -39258,28 +39319,28 @@
         <v>0.0824</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1773165455006624</v>
+        <v>-0.178335710333585</v>
       </c>
       <c r="J2" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K2" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01982482194141899</v>
+        <v>0.02011194166978092</v>
       </c>
       <c r="M2" t="n">
-        <v>7.705288710604838</v>
+        <v>7.697898409009037</v>
       </c>
       <c r="N2" t="n">
-        <v>89.61515322982908</v>
+        <v>89.49071542960513</v>
       </c>
       <c r="O2" t="n">
-        <v>9.466528045161493</v>
+        <v>9.459953246692351</v>
       </c>
       <c r="P2" t="n">
-        <v>357.1618120172773</v>
+        <v>357.172152734974</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39336,28 +39397,28 @@
         <v>0.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0602248610275824</v>
+        <v>0.05953194215796681</v>
       </c>
       <c r="J3" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K3" t="n">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004754971005251907</v>
+        <v>0.0004662023264682125</v>
       </c>
       <c r="M3" t="n">
-        <v>17.63336283640732</v>
+        <v>17.60902413115954</v>
       </c>
       <c r="N3" t="n">
-        <v>435.5909270969597</v>
+        <v>434.9075521635862</v>
       </c>
       <c r="O3" t="n">
-        <v>20.87081519962648</v>
+        <v>20.85443722960623</v>
       </c>
       <c r="P3" t="n">
-        <v>339.5101448965104</v>
+        <v>339.5172254068414</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39414,28 +39475,28 @@
         <v>0.0453</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1970886642382823</v>
+        <v>0.1945327309164445</v>
       </c>
       <c r="J4" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K4" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02388075609811069</v>
+        <v>0.02332979906210342</v>
       </c>
       <c r="M4" t="n">
-        <v>7.84568454314733</v>
+        <v>7.847080557129078</v>
       </c>
       <c r="N4" t="n">
-        <v>91.2611308821983</v>
+        <v>91.22711907119567</v>
       </c>
       <c r="O4" t="n">
-        <v>9.553069186507459</v>
+        <v>9.551288869634071</v>
       </c>
       <c r="P4" t="n">
-        <v>356.6885343126486</v>
+        <v>356.714497733993</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39492,28 +39553,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1950783094905881</v>
+        <v>0.1948910776490824</v>
       </c>
       <c r="J5" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K5" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02979175210411455</v>
+        <v>0.02983445583731614</v>
       </c>
       <c r="M5" t="n">
-        <v>6.812969240023715</v>
+        <v>6.803254616621762</v>
       </c>
       <c r="N5" t="n">
-        <v>71.43305935293994</v>
+        <v>71.32044668117169</v>
       </c>
       <c r="O5" t="n">
-        <v>8.451808052300995</v>
+        <v>8.445143378366746</v>
       </c>
       <c r="P5" t="n">
-        <v>359.2355498055093</v>
+        <v>359.2374498956091</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39570,28 +39631,28 @@
         <v>0.0466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04096789099221</v>
+        <v>0.04174936528079167</v>
       </c>
       <c r="J6" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K6" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001088221622628782</v>
+        <v>0.001134097488295516</v>
       </c>
       <c r="M6" t="n">
-        <v>7.492580523872719</v>
+        <v>7.477131228527723</v>
       </c>
       <c r="N6" t="n">
-        <v>88.79926366489785</v>
+        <v>88.64596438800515</v>
       </c>
       <c r="O6" t="n">
-        <v>9.423336121825319</v>
+        <v>9.415198584629278</v>
       </c>
       <c r="P6" t="n">
-        <v>357.2729776932466</v>
+        <v>357.2650777412472</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39648,28 +39709,28 @@
         <v>0.0487</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02414794650542968</v>
+        <v>-0.0247659221977341</v>
       </c>
       <c r="J7" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K7" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0005693793300205474</v>
+        <v>0.0006008524172812502</v>
       </c>
       <c r="M7" t="n">
-        <v>6.136072740389196</v>
+        <v>6.129173883781825</v>
       </c>
       <c r="N7" t="n">
-        <v>58.99615818440613</v>
+        <v>58.90912682026258</v>
       </c>
       <c r="O7" t="n">
-        <v>7.680895662903261</v>
+        <v>7.675228128222807</v>
       </c>
       <c r="P7" t="n">
-        <v>359.9496602830727</v>
+        <v>359.9559317029628</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39726,28 +39787,28 @@
         <v>0.0425</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.231968574391541</v>
+        <v>-0.2302426453569209</v>
       </c>
       <c r="J8" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K8" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01762839784892511</v>
+        <v>0.01742480904476473</v>
       </c>
       <c r="M8" t="n">
-        <v>10.48942029456206</v>
+        <v>10.48164127671012</v>
       </c>
       <c r="N8" t="n">
-        <v>172.8357705423986</v>
+        <v>172.6122902201493</v>
       </c>
       <c r="O8" t="n">
-        <v>13.14670188839766</v>
+        <v>13.13819965673187</v>
       </c>
       <c r="P8" t="n">
-        <v>339.4232072086178</v>
+        <v>339.4056919150369</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -39808,28 +39869,28 @@
         <v>0.0912</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.007416676746140558</v>
+        <v>-0.008513141457146055</v>
       </c>
       <c r="J9" t="n">
+        <v>633</v>
+      </c>
+      <c r="K9" t="n">
         <v>632</v>
       </c>
-      <c r="K9" t="n">
-        <v>631</v>
-      </c>
       <c r="L9" t="n">
-        <v>3.850365444024728e-05</v>
+        <v>5.088969178790315e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>7.210971425259382</v>
+        <v>7.205062250385321</v>
       </c>
       <c r="N9" t="n">
-        <v>82.22583320078002</v>
+        <v>82.11604148464238</v>
       </c>
       <c r="O9" t="n">
-        <v>9.067846116955229</v>
+        <v>9.061790192044969</v>
       </c>
       <c r="P9" t="n">
-        <v>345.3441482153308</v>
+        <v>345.3552809042723</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39886,28 +39947,28 @@
         <v>0.1192</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09321099523426597</v>
+        <v>0.09445786151531088</v>
       </c>
       <c r="J10" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K10" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005351522790047469</v>
+        <v>0.005511971176666131</v>
       </c>
       <c r="M10" t="n">
-        <v>7.832524148546055</v>
+        <v>7.826822574349737</v>
       </c>
       <c r="N10" t="n">
-        <v>92.8184442979901</v>
+        <v>92.69802771791763</v>
       </c>
       <c r="O10" t="n">
-        <v>9.634232937706566</v>
+        <v>9.627981497589078</v>
       </c>
       <c r="P10" t="n">
-        <v>349.9157824361218</v>
+        <v>349.9031166461584</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -39964,28 +40025,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1461948828060484</v>
+        <v>-0.1439720788728285</v>
       </c>
       <c r="J11" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K11" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006589392677902373</v>
+        <v>0.006410628939134133</v>
       </c>
       <c r="M11" t="n">
-        <v>10.74556822165851</v>
+        <v>10.73970710910583</v>
       </c>
       <c r="N11" t="n">
-        <v>185.206190586349</v>
+        <v>184.9969219823047</v>
       </c>
       <c r="O11" t="n">
-        <v>13.60904811463127</v>
+        <v>13.60135735808396</v>
       </c>
       <c r="P11" t="n">
-        <v>366.345070159595</v>
+        <v>366.3224906992504</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40042,28 +40103,28 @@
         <v>0.0789</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9250461163885412</v>
+        <v>-0.9175858343909018</v>
       </c>
       <c r="J12" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K12" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05166692753538615</v>
+        <v>0.05099415833501331</v>
       </c>
       <c r="M12" t="n">
-        <v>25.22673156268298</v>
+        <v>25.22403801500851</v>
       </c>
       <c r="N12" t="n">
-        <v>907.7039558815716</v>
+        <v>907.1906672570406</v>
       </c>
       <c r="O12" t="n">
-        <v>30.12812566160682</v>
+        <v>30.11960602758676</v>
       </c>
       <c r="P12" t="n">
-        <v>349.9240164484032</v>
+        <v>349.8483000054968</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40120,28 +40181,28 @@
         <v>0.1373</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.03380626923308989</v>
+        <v>-0.02508746788306518</v>
       </c>
       <c r="J13" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K13" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L13" t="n">
-        <v>5.694038541204094e-05</v>
+        <v>3.143026982432851e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>28.34205506395368</v>
+        <v>28.33846044317113</v>
       </c>
       <c r="N13" t="n">
-        <v>1153.604952519378</v>
+        <v>1153.064372396057</v>
       </c>
       <c r="O13" t="n">
-        <v>33.96476045137633</v>
+        <v>33.95680156310451</v>
       </c>
       <c r="P13" t="n">
-        <v>318.2810796138564</v>
+        <v>318.1925131746877</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -40198,28 +40259,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.538593693637934</v>
+        <v>-1.527872890805173</v>
       </c>
       <c r="J14" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K14" t="n">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0710862991719976</v>
+        <v>0.07031895738914473</v>
       </c>
       <c r="M14" t="n">
-        <v>34.8808544925338</v>
+        <v>34.86846170179609</v>
       </c>
       <c r="N14" t="n">
-        <v>1785.862056785139</v>
+        <v>1784.951967298816</v>
       </c>
       <c r="O14" t="n">
-        <v>42.25946115114507</v>
+        <v>42.24869190044605</v>
       </c>
       <c r="P14" t="n">
-        <v>348.9904376411809</v>
+        <v>348.8813761020386</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -40257,7 +40318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O633"/>
+  <dimension ref="A1:O634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88824,7 +88885,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>-37.20554669038834,174.61224524811777</t>
+          <t>-37.20555566274729,174.61221990379462</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
@@ -88868,6 +88929,83 @@
         </is>
       </c>
       <c r="O633" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>-37.20815256461722,174.6137303656287</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>-37.2074577921823,174.61348143148163</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>-37.20685405237985,174.61297534010356</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>-37.206234148445425,174.6125148915065</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>-37.205557522869825,174.61221464948292</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>-37.20489588209225,174.6118720633784</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>-37.20417298625778,174.61170698376003</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>-37.203522001703924,174.6113389432649</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>-37.20291191364522,174.6108445455416</t>
+        </is>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>-37.20229597868175,174.61036688092688</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr">
+        <is>
+          <t>-37.20156359600768,174.6102351048124</t>
+        </is>
+      </c>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>-37.20088790804022,174.60993490057712</t>
+        </is>
+      </c>
+      <c r="N634" t="inlineStr">
+        <is>
+          <t>-37.200216129545176,174.6096230660023</t>
+        </is>
+      </c>
+      <c r="O634" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0196/nzd0196.xlsx
+++ b/data/nzd0196/nzd0196.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O634"/>
+  <dimension ref="A1:O637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32704,7 +32704,7 @@
         <v>338.94</v>
       </c>
       <c r="I634" t="n">
-        <v>341.56</v>
+        <v>343.66</v>
       </c>
       <c r="J634" t="n">
         <v>356.47</v>
@@ -32724,6 +32724,159 @@
       <c r="O634" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:12:14+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>349.54</v>
+      </c>
+      <c r="C635" t="n">
+        <v>339.44</v>
+      </c>
+      <c r="D635" t="n">
+        <v>353.91</v>
+      </c>
+      <c r="E635" t="n">
+        <v>364.1</v>
+      </c>
+      <c r="F635" t="n">
+        <v>358.39</v>
+      </c>
+      <c r="G635" t="n">
+        <v>357.26</v>
+      </c>
+      <c r="H635" t="n">
+        <v>338.35</v>
+      </c>
+      <c r="I635" t="n">
+        <v>343.87</v>
+      </c>
+      <c r="J635" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="K635" t="n">
+        <v>370.4</v>
+      </c>
+      <c r="L635" t="n">
+        <v>351.06</v>
+      </c>
+      <c r="M635" t="n">
+        <v>347.12</v>
+      </c>
+      <c r="N635" t="n">
+        <v>344.29</v>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>349.75</v>
+      </c>
+      <c r="C636" t="n">
+        <v>342.38</v>
+      </c>
+      <c r="D636" t="n">
+        <v>354.44</v>
+      </c>
+      <c r="E636" t="n">
+        <v>365.06</v>
+      </c>
+      <c r="F636" t="n">
+        <v>360.56</v>
+      </c>
+      <c r="G636" t="n">
+        <v>358.64</v>
+      </c>
+      <c r="H636" t="n">
+        <v>340.63</v>
+      </c>
+      <c r="I636" t="n">
+        <v>346</v>
+      </c>
+      <c r="J636" t="n">
+        <v>358.12</v>
+      </c>
+      <c r="K636" t="n">
+        <v>371.48</v>
+      </c>
+      <c r="L636" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="M636" t="n">
+        <v>355.03</v>
+      </c>
+      <c r="N636" t="n">
+        <v>349.71</v>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>350.65</v>
+      </c>
+      <c r="C637" t="n">
+        <v>343.29</v>
+      </c>
+      <c r="D637" t="n">
+        <v>353.97</v>
+      </c>
+      <c r="E637" t="n">
+        <v>365.99</v>
+      </c>
+      <c r="F637" t="n">
+        <v>362.49</v>
+      </c>
+      <c r="G637" t="n">
+        <v>360.56</v>
+      </c>
+      <c r="H637" t="n">
+        <v>342.92</v>
+      </c>
+      <c r="I637" t="n">
+        <v>347.56</v>
+      </c>
+      <c r="J637" t="n">
+        <v>358.22</v>
+      </c>
+      <c r="K637" t="n">
+        <v>370.72</v>
+      </c>
+      <c r="L637" t="n">
+        <v>357.8</v>
+      </c>
+      <c r="M637" t="n">
+        <v>356.65</v>
+      </c>
+      <c r="N637" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -32738,7 +32891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B641"/>
+  <dimension ref="A1:B644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39151,6 +39304,36 @@
       </c>
       <c r="B641" t="n">
         <v>-0.47</v>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>0.85</v>
       </c>
     </row>
   </sheetData>
@@ -39319,28 +39502,28 @@
         <v>0.0824</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.178335710333585</v>
+        <v>-0.1805679591681258</v>
       </c>
       <c r="J2" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K2" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02011194166978092</v>
+        <v>0.02080751673215375</v>
       </c>
       <c r="M2" t="n">
-        <v>7.697898409009037</v>
+        <v>7.671943277596228</v>
       </c>
       <c r="N2" t="n">
-        <v>89.49071542960513</v>
+        <v>89.09672147469867</v>
       </c>
       <c r="O2" t="n">
-        <v>9.459953246692351</v>
+        <v>9.439105967976982</v>
       </c>
       <c r="P2" t="n">
-        <v>357.172152734974</v>
+        <v>357.194842596441</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39397,28 +39580,28 @@
         <v>0.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05953194215796681</v>
+        <v>0.06008795928937453</v>
       </c>
       <c r="J3" t="n">
+        <v>636</v>
+      </c>
+      <c r="K3" t="n">
         <v>633</v>
       </c>
-      <c r="K3" t="n">
-        <v>630</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0004662023264682125</v>
+        <v>0.0004797898331930783</v>
       </c>
       <c r="M3" t="n">
-        <v>17.60902413115954</v>
+        <v>17.5335987037675</v>
       </c>
       <c r="N3" t="n">
-        <v>434.9075521635862</v>
+        <v>432.8608470462436</v>
       </c>
       <c r="O3" t="n">
-        <v>20.85443722960623</v>
+        <v>20.80530814590939</v>
       </c>
       <c r="P3" t="n">
-        <v>339.5172254068414</v>
+        <v>339.511519826472</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39475,28 +39658,28 @@
         <v>0.0453</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1945327309164445</v>
+        <v>0.1874995489361495</v>
       </c>
       <c r="J4" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K4" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02332979906210342</v>
+        <v>0.02186037401860974</v>
       </c>
       <c r="M4" t="n">
-        <v>7.847080557129078</v>
+        <v>7.847970006412073</v>
       </c>
       <c r="N4" t="n">
-        <v>91.22711907119567</v>
+        <v>91.07718883957894</v>
       </c>
       <c r="O4" t="n">
-        <v>9.551288869634071</v>
+        <v>9.543436951097803</v>
       </c>
       <c r="P4" t="n">
-        <v>356.714497733993</v>
+        <v>356.7860809587548</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39553,28 +39736,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1948910776490824</v>
+        <v>0.195479579376492</v>
       </c>
       <c r="J5" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K5" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02983445583731614</v>
+        <v>0.03030470592573664</v>
       </c>
       <c r="M5" t="n">
-        <v>6.803254616621762</v>
+        <v>6.774702907549503</v>
       </c>
       <c r="N5" t="n">
-        <v>71.32044668117169</v>
+        <v>70.98770618699093</v>
       </c>
       <c r="O5" t="n">
-        <v>8.445143378366746</v>
+        <v>8.425420238005398</v>
       </c>
       <c r="P5" t="n">
-        <v>359.2374498956091</v>
+        <v>359.231459644657</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39631,28 +39814,28 @@
         <v>0.0466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04174936528079167</v>
+        <v>0.04366021060194694</v>
       </c>
       <c r="J6" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K6" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001134097488295516</v>
+        <v>0.001252323028782532</v>
       </c>
       <c r="M6" t="n">
-        <v>7.477131228527723</v>
+        <v>7.451966400023743</v>
       </c>
       <c r="N6" t="n">
-        <v>88.64596438800515</v>
+        <v>88.26046380145138</v>
       </c>
       <c r="O6" t="n">
-        <v>9.415198584629278</v>
+        <v>9.394704029475935</v>
       </c>
       <c r="P6" t="n">
-        <v>357.2650777412472</v>
+        <v>357.245634179167</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39709,28 +39892,28 @@
         <v>0.0487</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0247659221977341</v>
+        <v>-0.0251984775361048</v>
       </c>
       <c r="J7" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K7" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0006008524172812502</v>
+        <v>0.0006282552825732646</v>
       </c>
       <c r="M7" t="n">
-        <v>6.129173883781825</v>
+        <v>6.106131236306255</v>
       </c>
       <c r="N7" t="n">
-        <v>58.90912682026258</v>
+        <v>58.64009414422303</v>
       </c>
       <c r="O7" t="n">
-        <v>7.675228128222807</v>
+        <v>7.657682034677532</v>
       </c>
       <c r="P7" t="n">
-        <v>359.9559317029628</v>
+        <v>359.9603191921281</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39787,28 +39970,28 @@
         <v>0.0425</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2302426453569209</v>
+        <v>-0.2236015635146565</v>
       </c>
       <c r="J8" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K8" t="n">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01742480904476473</v>
+        <v>0.01659025149627258</v>
       </c>
       <c r="M8" t="n">
-        <v>10.48164127671012</v>
+        <v>10.46576882992752</v>
       </c>
       <c r="N8" t="n">
-        <v>172.6122902201493</v>
+        <v>172.0625475895783</v>
       </c>
       <c r="O8" t="n">
-        <v>13.13819965673187</v>
+        <v>13.11726143635089</v>
       </c>
       <c r="P8" t="n">
-        <v>339.4056919150369</v>
+        <v>339.338148421221</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -39869,28 +40052,28 @@
         <v>0.0912</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.008513141457146055</v>
+        <v>-0.007260436023253909</v>
       </c>
       <c r="J9" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K9" t="n">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="L9" t="n">
-        <v>5.088969178790315e-05</v>
+        <v>3.739528269630643e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>7.205062250385321</v>
+        <v>7.175072288085778</v>
       </c>
       <c r="N9" t="n">
-        <v>82.11604148464238</v>
+        <v>81.72427025780131</v>
       </c>
       <c r="O9" t="n">
-        <v>9.061790192044969</v>
+        <v>9.040147690043637</v>
       </c>
       <c r="P9" t="n">
-        <v>345.3552809042723</v>
+        <v>345.3425374905564</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -39947,28 +40130,28 @@
         <v>0.1192</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09445786151531088</v>
+        <v>0.0991977384277694</v>
       </c>
       <c r="J10" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K10" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005511971176666131</v>
+        <v>0.006128745237249822</v>
       </c>
       <c r="M10" t="n">
-        <v>7.826822574349737</v>
+        <v>7.815128252119752</v>
       </c>
       <c r="N10" t="n">
-        <v>92.69802771791763</v>
+        <v>92.39064537767653</v>
       </c>
       <c r="O10" t="n">
-        <v>9.627981497589078</v>
+        <v>9.612005273494004</v>
       </c>
       <c r="P10" t="n">
-        <v>349.9031166461584</v>
+        <v>349.8548688154142</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40025,28 +40208,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1439720788728285</v>
+        <v>-0.1363984938367502</v>
       </c>
       <c r="J11" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K11" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="L11" t="n">
-        <v>0.006410628939134133</v>
+        <v>0.005806004570951595</v>
       </c>
       <c r="M11" t="n">
-        <v>10.73970710910583</v>
+        <v>10.72667587559801</v>
       </c>
       <c r="N11" t="n">
-        <v>184.9969219823047</v>
+        <v>184.4500637186387</v>
       </c>
       <c r="O11" t="n">
-        <v>13.60135735808396</v>
+        <v>13.58123940289098</v>
       </c>
       <c r="P11" t="n">
-        <v>366.3224906992504</v>
+        <v>366.2454058542827</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40103,28 +40286,28 @@
         <v>0.0789</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9175858343909018</v>
+        <v>-0.8907318888344365</v>
       </c>
       <c r="J12" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K12" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="L12" t="n">
-        <v>0.05099415833501331</v>
+        <v>0.04845353947253284</v>
       </c>
       <c r="M12" t="n">
-        <v>25.22403801500851</v>
+        <v>25.23938909448215</v>
       </c>
       <c r="N12" t="n">
-        <v>907.1906672570406</v>
+        <v>906.9849158497219</v>
       </c>
       <c r="O12" t="n">
-        <v>30.11960602758676</v>
+        <v>30.11619026121534</v>
       </c>
       <c r="P12" t="n">
-        <v>349.8483000054968</v>
+        <v>349.5751891420593</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40181,28 +40364,28 @@
         <v>0.1373</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.02508746788306518</v>
+        <v>0.006995221233567822</v>
       </c>
       <c r="J13" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K13" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="L13" t="n">
-        <v>3.143026982432851e-05</v>
+        <v>2.456050878008043e-06</v>
       </c>
       <c r="M13" t="n">
-        <v>28.33846044317113</v>
+        <v>28.35731719504972</v>
       </c>
       <c r="N13" t="n">
-        <v>1153.064372396057</v>
+        <v>1153.53394863711</v>
       </c>
       <c r="O13" t="n">
-        <v>33.95680156310451</v>
+        <v>33.9637151771874</v>
       </c>
       <c r="P13" t="n">
-        <v>318.1925131746877</v>
+        <v>317.8659449512585</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -40259,28 +40442,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.527872890805173</v>
+        <v>-1.490276791034205</v>
       </c>
       <c r="J14" t="n">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K14" t="n">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07031895738914473</v>
+        <v>0.06747965936385447</v>
       </c>
       <c r="M14" t="n">
-        <v>34.86846170179609</v>
+        <v>34.85413477401916</v>
       </c>
       <c r="N14" t="n">
-        <v>1784.951967298816</v>
+        <v>1784.565400754678</v>
       </c>
       <c r="O14" t="n">
-        <v>42.24869190044605</v>
+        <v>42.24411675907875</v>
       </c>
       <c r="P14" t="n">
-        <v>348.8813761020386</v>
+        <v>348.4981185690792</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -40318,7 +40501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O634"/>
+  <dimension ref="A1:O637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88977,7 +89160,7 @@
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>-37.203522001703924,174.6113389432649</t>
+          <t>-37.2035293637665,174.6113171477442</t>
         </is>
       </c>
       <c r="J634" t="inlineStr">
@@ -89008,6 +89191,237 @@
       <c r="O634" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:12:14+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>-37.20815406004768,174.6137261414531</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>-37.20745994413601,174.61347535284094</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>-37.206855438371065,174.61297142507013</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>-37.2062353155863,174.61251159465726</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>-37.20555719461292,174.61221557671445</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>-37.20489577267388,174.61187237245326</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>-37.204170873101226,174.6117130833786</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>-37.20353009997254,174.61131496819186</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>-37.20291226321848,174.61084350714023</t>
+        </is>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>-37.2022982159298,174.61036023519986</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr">
+        <is>
+          <t>-37.20156821032784,174.61022139812962</t>
+        </is>
+      </c>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>-37.200892032942676,174.6099226477306</t>
+        </is>
+      </c>
+      <c r="N635" t="inlineStr">
+        <is>
+          <t>-37.20021973007705,174.60961237080468</t>
+        </is>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-37.20815482599983,174.6137239778509</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-37.20747066742624,174.61344506266002</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>-37.20685737146386,174.61296596462853</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>-37.20623881700836,174.61250170410895</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>-37.20556510924958,174.61219322013065</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>-37.20490080591781,174.61185815500946</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>-37.20417903919607,174.61168951196936</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>-37.20353756720305,174.61129286130165</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>-37.2029176816029,174.61082741191785</t>
+        </is>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>-37.20230199128502,174.61034902053458</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr">
+        <is>
+          <t>-37.20158603836844,174.6101684404756</t>
+        </is>
+      </c>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>-37.20091968373988,174.60984051208834</t>
+        </is>
+      </c>
+      <c r="N636" t="inlineStr">
+        <is>
+          <t>-37.200238676549645,174.60955609120384</t>
+        </is>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-37.20815810865139,174.61371470526947</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-37.20747398653834,174.61343568712604</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>-37.20685565721177,174.61297080690693</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>-37.20624220901022,174.61249212263937</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>-37.20557214853124,174.61217333616037</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>-37.204907808689185,174.61183837421487</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>-37.20418724110251,174.6116658371715</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>-37.20354303615804,174.61127667033696</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>-37.202918031176004,174.61082637351632</t>
+        </is>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>-37.20229933455368,174.6103569123362</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr">
+        <is>
+          <t>-37.20159177130206,174.61015141095</t>
+        </is>
+      </c>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>-37.200925346728134,174.60982369036893</t>
+        </is>
+      </c>
+      <c r="N637" t="inlineStr">
+        <is>
+          <t>-37.20025786769172,174.60949908471514</t>
+        </is>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>

--- a/data/nzd0196/nzd0196.xlsx
+++ b/data/nzd0196/nzd0196.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O637"/>
+  <dimension ref="A1:O638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32875,6 +32875,57 @@
         <v>355.2</v>
       </c>
       <c r="O637" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:59+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>350.94</v>
+      </c>
+      <c r="C638" t="n">
+        <v>346.39</v>
+      </c>
+      <c r="D638" t="n">
+        <v>355.5</v>
+      </c>
+      <c r="E638" t="n">
+        <v>368.07</v>
+      </c>
+      <c r="F638" t="n">
+        <v>365.22</v>
+      </c>
+      <c r="G638" t="n">
+        <v>362.47</v>
+      </c>
+      <c r="H638" t="n">
+        <v>351</v>
+      </c>
+      <c r="I638" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="J638" t="n">
+        <v>362.48</v>
+      </c>
+      <c r="K638" t="n">
+        <v>377</v>
+      </c>
+      <c r="L638" t="n">
+        <v>373.72</v>
+      </c>
+      <c r="M638" t="n">
+        <v>372.69</v>
+      </c>
+      <c r="N638" t="n">
+        <v>371.4</v>
+      </c>
+      <c r="O638" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -32891,7 +32942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B644"/>
+  <dimension ref="A1:B645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39334,6 +39385,16 @@
       </c>
       <c r="B644" t="n">
         <v>0.85</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -39502,28 +39563,28 @@
         <v>0.0824</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1805679591681258</v>
+        <v>-0.1810056967785883</v>
       </c>
       <c r="J2" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K2" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02080751673215375</v>
+        <v>0.02097581835125195</v>
       </c>
       <c r="M2" t="n">
-        <v>7.671943277596228</v>
+        <v>7.661885669779411</v>
       </c>
       <c r="N2" t="n">
-        <v>89.09672147469867</v>
+        <v>88.95966375016715</v>
       </c>
       <c r="O2" t="n">
-        <v>9.439105967976982</v>
+        <v>9.431843072812818</v>
       </c>
       <c r="P2" t="n">
-        <v>357.194842596441</v>
+        <v>357.1993190966826</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -39580,28 +39641,28 @@
         <v>0.05</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06008795928937453</v>
+        <v>0.06170062155799071</v>
       </c>
       <c r="J3" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K3" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004797898331930783</v>
+        <v>0.0005075611728648788</v>
       </c>
       <c r="M3" t="n">
-        <v>17.5335987037675</v>
+        <v>17.51405357394295</v>
       </c>
       <c r="N3" t="n">
-        <v>432.8608470462436</v>
+        <v>432.2217562552495</v>
       </c>
       <c r="O3" t="n">
-        <v>20.80530814590939</v>
+        <v>20.78994363280597</v>
       </c>
       <c r="P3" t="n">
-        <v>339.511519826472</v>
+        <v>339.4949117749691</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -39658,28 +39719,28 @@
         <v>0.0453</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1874995489361495</v>
+        <v>0.1855892028722421</v>
       </c>
       <c r="J4" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K4" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02186037401860974</v>
+        <v>0.02148435671440418</v>
       </c>
       <c r="M4" t="n">
-        <v>7.847970006412073</v>
+        <v>7.845892181809334</v>
       </c>
       <c r="N4" t="n">
-        <v>91.07718883957894</v>
+        <v>90.99591102966957</v>
       </c>
       <c r="O4" t="n">
-        <v>9.543436951097803</v>
+        <v>9.53917769148209</v>
       </c>
       <c r="P4" t="n">
-        <v>356.7860809587548</v>
+        <v>356.8056389891386</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -39736,28 +39797,28 @@
         <v>0.0428</v>
       </c>
       <c r="I5" t="n">
-        <v>0.195479579376492</v>
+        <v>0.1965840187552158</v>
       </c>
       <c r="J5" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K5" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03030470592573664</v>
+        <v>0.0307306560748335</v>
       </c>
       <c r="M5" t="n">
-        <v>6.774702907549503</v>
+        <v>6.769060692850796</v>
       </c>
       <c r="N5" t="n">
-        <v>70.98770618699093</v>
+        <v>70.89661721275742</v>
       </c>
       <c r="O5" t="n">
-        <v>8.425420238005398</v>
+        <v>8.420012898609919</v>
       </c>
       <c r="P5" t="n">
-        <v>359.231459644657</v>
+        <v>359.2201628592951</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -39814,28 +39875,28 @@
         <v>0.0466</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04366021060194694</v>
+        <v>0.0457310957837316</v>
       </c>
       <c r="J6" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K6" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001252323028782532</v>
+        <v>0.001377338768084546</v>
       </c>
       <c r="M6" t="n">
-        <v>7.451966400023743</v>
+        <v>7.451259540331942</v>
       </c>
       <c r="N6" t="n">
-        <v>88.26046380145138</v>
+        <v>88.1942581486197</v>
       </c>
       <c r="O6" t="n">
-        <v>9.394704029475935</v>
+        <v>9.391179805999867</v>
       </c>
       <c r="P6" t="n">
-        <v>357.245634179167</v>
+        <v>357.2244520791275</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -39892,28 +39953,28 @@
         <v>0.0487</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0251984775361048</v>
+        <v>-0.02423300659765781</v>
       </c>
       <c r="J7" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K7" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0006282552825732646</v>
+        <v>0.0005828949607996625</v>
       </c>
       <c r="M7" t="n">
-        <v>6.106131236306255</v>
+        <v>6.102111262048336</v>
       </c>
       <c r="N7" t="n">
-        <v>58.64009414422303</v>
+        <v>58.56356808296673</v>
       </c>
       <c r="O7" t="n">
-        <v>7.657682034677532</v>
+        <v>7.652683717687981</v>
       </c>
       <c r="P7" t="n">
-        <v>359.9603191921281</v>
+        <v>359.9504438488771</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -39970,28 +40031,28 @@
         <v>0.0425</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2236015635146565</v>
+        <v>-0.218247671793078</v>
       </c>
       <c r="J8" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K8" t="n">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01659025149627258</v>
+        <v>0.0158269463786288</v>
       </c>
       <c r="M8" t="n">
-        <v>10.46576882992752</v>
+        <v>10.47631245805539</v>
       </c>
       <c r="N8" t="n">
-        <v>172.0625475895783</v>
+        <v>172.2780821814501</v>
       </c>
       <c r="O8" t="n">
-        <v>13.11726143635089</v>
+        <v>13.12547455071435</v>
       </c>
       <c r="P8" t="n">
-        <v>339.338148421221</v>
+        <v>339.2833860080053</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -40052,28 +40113,28 @@
         <v>0.0912</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.007260436023253909</v>
+        <v>-0.005619539855270836</v>
       </c>
       <c r="J9" t="n">
+        <v>637</v>
+      </c>
+      <c r="K9" t="n">
         <v>636</v>
       </c>
-      <c r="K9" t="n">
-        <v>635</v>
-      </c>
       <c r="L9" t="n">
-        <v>3.739528269630643e-05</v>
+        <v>2.246690944718299e-05</v>
       </c>
       <c r="M9" t="n">
-        <v>7.175072288085778</v>
+        <v>7.172498935936979</v>
       </c>
       <c r="N9" t="n">
-        <v>81.72427025780131</v>
+        <v>81.64138349602764</v>
       </c>
       <c r="O9" t="n">
-        <v>9.040147690043637</v>
+        <v>9.035562157166959</v>
       </c>
       <c r="P9" t="n">
-        <v>345.3425374905564</v>
+        <v>345.3257457359296</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -40130,28 +40191,28 @@
         <v>0.1192</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0991977384277694</v>
+        <v>0.1022319805772376</v>
       </c>
       <c r="J10" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K10" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006128745237249822</v>
+        <v>0.00651818406831306</v>
       </c>
       <c r="M10" t="n">
-        <v>7.815128252119752</v>
+        <v>7.818812641437027</v>
       </c>
       <c r="N10" t="n">
-        <v>92.39064537767653</v>
+        <v>92.40126085126906</v>
       </c>
       <c r="O10" t="n">
-        <v>9.612005273494004</v>
+        <v>9.612557456331226</v>
       </c>
       <c r="P10" t="n">
-        <v>349.8548688154142</v>
+        <v>349.8238043913958</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -40208,28 +40269,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1363984938367502</v>
+        <v>-0.1320267346762991</v>
       </c>
       <c r="J11" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K11" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005806004570951595</v>
+        <v>0.005450837363489613</v>
       </c>
       <c r="M11" t="n">
-        <v>10.72667587559801</v>
+        <v>10.73143581879801</v>
       </c>
       <c r="N11" t="n">
-        <v>184.4500637186387</v>
+        <v>184.4836330484251</v>
       </c>
       <c r="O11" t="n">
-        <v>13.58123940289098</v>
+        <v>13.58247521803096</v>
       </c>
       <c r="P11" t="n">
-        <v>366.2454058542827</v>
+        <v>366.2006479959522</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -40286,28 +40347,28 @@
         <v>0.0789</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8907318888344365</v>
+        <v>-0.8760996200224367</v>
       </c>
       <c r="J12" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K12" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L12" t="n">
-        <v>0.04845353947253284</v>
+        <v>0.04692337066069074</v>
       </c>
       <c r="M12" t="n">
-        <v>25.23938909448215</v>
+        <v>25.27254298074376</v>
       </c>
       <c r="N12" t="n">
-        <v>906.9849158497219</v>
+        <v>909.1717102464754</v>
       </c>
       <c r="O12" t="n">
-        <v>30.11619026121534</v>
+        <v>30.15247436358209</v>
       </c>
       <c r="P12" t="n">
-        <v>349.5751891420593</v>
+        <v>349.4254997162102</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -40364,28 +40425,28 @@
         <v>0.1373</v>
       </c>
       <c r="I13" t="n">
-        <v>0.006995221233567822</v>
+        <v>0.02360354154885108</v>
       </c>
       <c r="J13" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K13" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L13" t="n">
-        <v>2.456050878008043e-06</v>
+        <v>2.794539146544484e-05</v>
       </c>
       <c r="M13" t="n">
-        <v>28.35731719504972</v>
+        <v>28.39174073147831</v>
       </c>
       <c r="N13" t="n">
-        <v>1153.53394863711</v>
+        <v>1156.386607247151</v>
       </c>
       <c r="O13" t="n">
-        <v>33.9637151771874</v>
+        <v>34.00568492542314</v>
       </c>
       <c r="P13" t="n">
-        <v>317.8659449512585</v>
+        <v>317.6959097730847</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -40442,28 +40503,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.490276791034205</v>
+        <v>-1.471182140545927</v>
       </c>
       <c r="J14" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="K14" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L14" t="n">
-        <v>0.06747965936385447</v>
+        <v>0.06587091183397353</v>
       </c>
       <c r="M14" t="n">
-        <v>34.85413477401916</v>
+        <v>34.87625269603024</v>
       </c>
       <c r="N14" t="n">
-        <v>1784.565400754678</v>
+        <v>1787.930694226084</v>
       </c>
       <c r="O14" t="n">
-        <v>42.24411675907875</v>
+        <v>42.28392950313493</v>
       </c>
       <c r="P14" t="n">
-        <v>348.4981185690792</v>
+        <v>348.3023199165811</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -40501,7 +40562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O637"/>
+  <dimension ref="A1:O638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89425,6 +89486,83 @@
         </is>
       </c>
     </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:59+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-37.20815916639452,174.61371171743752</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-37.20748529339832,174.61340374848749</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-37.206861237648695,174.61295504374445</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-37.20624979542025,174.6124706931128</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-37.205582105644304,174.61214521012343</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>-37.204914774984594,174.61181869644153</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>-37.20421618054331,174.61158230334487</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>-37.20355351831572,174.61124563764795</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>-37.20293292298243,174.61078213760217</t>
+        </is>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>-37.20232128752893,174.6102917011163</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr">
+        <is>
+          <t>-37.20164742258213,174.60998609980788</t>
+        </is>
+      </c>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>-37.20098141717721,174.60965713443946</t>
+        </is>
+      </c>
+      <c r="N638" t="inlineStr">
+        <is>
+          <t>-37.200314497134926,174.60933086867365</t>
+        </is>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
